--- a/estimate-boq-v2/src/assets/templates/boq-master.xlsx
+++ b/estimate-boq-v2/src/assets/templates/boq-master.xlsx
@@ -5364,7 +5364,7 @@
       <c r="J26" s="547" t="n"/>
       <c r="K26" s="547" t="n"/>
       <c r="N26" s="548">
-        <f>FLOOR(V26,0.0001)</f>
+        <f>CEILING(V26,0.0001)</f>
         <v/>
       </c>
       <c r="O26" s="549" t="n"/>
